--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="853" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2198E741-27C7-4ACF-A7A1-6E6A0EC74CE9}"/>
+  <xr:revisionPtr revIDLastSave="928" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA72FAEE-99DE-4426-AE75-04B1C7E1641F}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="900" windowWidth="22632" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11328" yWindow="1524" windowWidth="10068" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="159">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -516,6 +516,18 @@
   <si>
     <t>Medicine</t>
   </si>
+  <si>
+    <t>Vehicle Insur</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>ADVANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFFIF </t>
+  </si>
 </sst>
 </file>
 
@@ -532,7 +544,7 @@
     <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -600,6 +612,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -621,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -654,6 +673,7 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H509"/>
+  <dimension ref="A1:H526"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -11576,10 +11596,345 @@
         <v>0</v>
       </c>
       <c r="F509" s="6">
-        <f t="shared" ref="F509" si="90">F508-D509+E509</f>
+        <f t="shared" ref="F509:F515" si="90">F508-D509+E509</f>
         <v>131330.79379200039</v>
       </c>
       <c r="G509" s="22"/>
+    </row>
+    <row r="510" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B510" s="28">
+        <v>46067</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D510" s="5">
+        <v>20</v>
+      </c>
+      <c r="E510" s="5">
+        <v>0</v>
+      </c>
+      <c r="F510" s="6">
+        <f t="shared" si="90"/>
+        <v>131310.79379200039</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A511" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B511" s="28">
+        <v>46068</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D511" s="5">
+        <v>432</v>
+      </c>
+      <c r="E511" s="5">
+        <v>0</v>
+      </c>
+      <c r="F511" s="6">
+        <f t="shared" si="90"/>
+        <v>130878.79379200039</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B512" s="28">
+        <v>46067</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D512" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E512" s="5">
+        <v>0</v>
+      </c>
+      <c r="F512" s="6">
+        <f t="shared" si="90"/>
+        <v>125878.79379200039</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B513" s="28">
+        <v>46070</v>
+      </c>
+      <c r="C513" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D513" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E513" s="5">
+        <v>0</v>
+      </c>
+      <c r="F513" s="6">
+        <f t="shared" si="90"/>
+        <v>120878.79379200039</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B514" s="28">
+        <v>46079</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D514" s="5">
+        <v>11600</v>
+      </c>
+      <c r="E514" s="5">
+        <v>0</v>
+      </c>
+      <c r="F514" s="6">
+        <f t="shared" si="90"/>
+        <v>109278.79379200039</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B515" s="29">
+        <v>46080</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D515" s="7">
+        <v>0</v>
+      </c>
+      <c r="E515" s="5">
+        <v>14313.6</v>
+      </c>
+      <c r="F515" s="30">
+        <f t="shared" si="90"/>
+        <v>123592.3937920004</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B516" s="29">
+        <v>46080</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D516" s="7">
+        <v>14313.6</v>
+      </c>
+      <c r="E516" s="5">
+        <v>0</v>
+      </c>
+      <c r="F516" s="30">
+        <f t="shared" ref="F516:F526" si="91">F515-D516+E516</f>
+        <v>109278.79379200039</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B517" s="29">
+        <v>46083</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D517" s="7">
+        <v>4840</v>
+      </c>
+      <c r="E517" s="5">
+        <v>0</v>
+      </c>
+      <c r="F517" s="6">
+        <f t="shared" si="91"/>
+        <v>104438.79379200039</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B518" s="29">
+        <v>46085</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D518" s="5">
+        <v>0</v>
+      </c>
+      <c r="E518" s="5">
+        <v>30256.6</v>
+      </c>
+      <c r="F518" s="6">
+        <f t="shared" si="91"/>
+        <v>134695.3937920004</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B519" s="29">
+        <v>46085</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D519" s="5">
+        <v>6051.32</v>
+      </c>
+      <c r="E519" s="5">
+        <v>0</v>
+      </c>
+      <c r="F519" s="6">
+        <f t="shared" si="91"/>
+        <v>128644.07379200039</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A520" s="28">
+        <v>46080</v>
+      </c>
+      <c r="B520" s="28">
+        <v>46083</v>
+      </c>
+      <c r="C520" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D520" s="32">
+        <v>38084.17</v>
+      </c>
+      <c r="E520" s="7">
+        <v>0</v>
+      </c>
+      <c r="F520" s="6">
+        <f t="shared" si="91"/>
+        <v>90559.90379200039</v>
+      </c>
+      <c r="G520" s="22"/>
+    </row>
+    <row r="521" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A521" s="28">
+        <v>46080</v>
+      </c>
+      <c r="B521" s="28">
+        <v>46083</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D521" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E521" s="5">
+        <v>0</v>
+      </c>
+      <c r="F521" s="6">
+        <f t="shared" si="91"/>
+        <v>90544.923792000394</v>
+      </c>
+      <c r="G521" s="22"/>
+    </row>
+    <row r="522" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A522" s="28"/>
+      <c r="B522" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D522" s="5">
+        <v>1436.61</v>
+      </c>
+      <c r="E522" s="5">
+        <v>0</v>
+      </c>
+      <c r="F522" s="6">
+        <f t="shared" si="91"/>
+        <v>89108.313792000394</v>
+      </c>
+      <c r="G522" s="22"/>
+    </row>
+    <row r="523" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A523" s="28">
+        <v>46085</v>
+      </c>
+      <c r="B523" s="28">
+        <v>46087</v>
+      </c>
+      <c r="C523" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D523" s="32">
+        <v>0</v>
+      </c>
+      <c r="E523" s="7">
+        <v>193818.09</v>
+      </c>
+      <c r="F523" s="6">
+        <f t="shared" si="91"/>
+        <v>282926.40379200038</v>
+      </c>
+      <c r="G523" s="22"/>
+    </row>
+    <row r="524" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A524" s="28">
+        <v>46085</v>
+      </c>
+      <c r="B524" s="28">
+        <v>46087</v>
+      </c>
+      <c r="C524" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D524" s="32">
+        <v>0</v>
+      </c>
+      <c r="E524" s="7">
+        <v>42405.86</v>
+      </c>
+      <c r="F524" s="6">
+        <f t="shared" si="91"/>
+        <v>325332.26379200036</v>
+      </c>
+      <c r="G524" s="22"/>
+    </row>
+    <row r="525" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A525" s="28">
+        <v>46085</v>
+      </c>
+      <c r="B525" s="28">
+        <v>46087</v>
+      </c>
+      <c r="C525" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D525" s="32">
+        <v>32571.99</v>
+      </c>
+      <c r="E525" s="7">
+        <v>0</v>
+      </c>
+      <c r="F525" s="6">
+        <f t="shared" si="91"/>
+        <v>292760.27379200037</v>
+      </c>
+      <c r="G525" s="22"/>
+    </row>
+    <row r="526" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A526" s="28">
+        <v>46085</v>
+      </c>
+      <c r="B526" s="28">
+        <v>46087</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D526" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E526" s="5">
+        <v>0</v>
+      </c>
+      <c r="F526" s="6">
+        <f t="shared" si="91"/>
+        <v>292745.29379200039</v>
+      </c>
+      <c r="G526" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="928" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA72FAEE-99DE-4426-AE75-04B1C7E1641F}"/>
+  <xr:revisionPtr revIDLastSave="957" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2574D36B-E1ED-43BB-8D5A-8B07275B197F}"/>
   <bookViews>
-    <workbookView xWindow="11328" yWindow="1524" windowWidth="10068" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13104" yWindow="1704" windowWidth="10068" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -528,6 +528,9 @@
   <si>
     <t xml:space="preserve">TFFIF </t>
   </si>
+  <si>
+    <t xml:space="preserve">SCC </t>
+  </si>
 </sst>
 </file>
 
@@ -982,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H526"/>
+  <dimension ref="A1:H532"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -11862,11 +11865,11 @@
         <v>0</v>
       </c>
       <c r="E523" s="7">
-        <v>193818.09</v>
+        <v>193819.76</v>
       </c>
       <c r="F523" s="6">
         <f t="shared" si="91"/>
-        <v>282926.40379200038</v>
+        <v>282928.07379200042</v>
       </c>
       <c r="G523" s="22"/>
     </row>
@@ -11888,7 +11891,7 @@
       </c>
       <c r="F524" s="6">
         <f t="shared" si="91"/>
-        <v>325332.26379200036</v>
+        <v>325333.9337920004</v>
       </c>
       <c r="G524" s="22"/>
     </row>
@@ -11910,7 +11913,7 @@
       </c>
       <c r="F525" s="6">
         <f t="shared" si="91"/>
-        <v>292760.27379200037</v>
+        <v>292761.94379200041</v>
       </c>
       <c r="G525" s="22"/>
     </row>
@@ -11932,9 +11935,125 @@
       </c>
       <c r="F526" s="6">
         <f t="shared" si="91"/>
-        <v>292745.29379200039</v>
+        <v>292746.96379200043</v>
       </c>
       <c r="G526" s="22"/>
+    </row>
+    <row r="527" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B527" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D527" s="5">
+        <v>0</v>
+      </c>
+      <c r="E527" s="5">
+        <v>8999.1</v>
+      </c>
+      <c r="F527" s="6">
+        <f t="shared" ref="F527:F531" si="92">F526-D527+E527</f>
+        <v>301746.06379200041</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B528" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D528" s="5">
+        <v>12000</v>
+      </c>
+      <c r="E528" s="5">
+        <v>0</v>
+      </c>
+      <c r="F528" s="6">
+        <f t="shared" si="92"/>
+        <v>289746.06379200041</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B529" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D529" s="7">
+        <v>12600</v>
+      </c>
+      <c r="E529" s="5">
+        <v>0</v>
+      </c>
+      <c r="F529" s="30">
+        <f t="shared" si="92"/>
+        <v>277146.06379200041</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A530" s="28">
+        <v>46090</v>
+      </c>
+      <c r="B530" s="28">
+        <v>46092</v>
+      </c>
+      <c r="C530" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D530" s="32">
+        <v>0</v>
+      </c>
+      <c r="E530" s="7">
+        <v>102971.43</v>
+      </c>
+      <c r="F530" s="6">
+        <f t="shared" si="92"/>
+        <v>380117.4937920004</v>
+      </c>
+      <c r="G530" s="22"/>
+    </row>
+    <row r="531" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A531" s="28">
+        <v>46090</v>
+      </c>
+      <c r="B531" s="28">
+        <v>46092</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D531" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E531" s="5">
+        <v>0</v>
+      </c>
+      <c r="F531" s="6">
+        <f t="shared" si="92"/>
+        <v>380102.51379200042</v>
+      </c>
+      <c r="G531" s="22"/>
+    </row>
+    <row r="532" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B532" s="28">
+        <v>46093</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D532" s="5">
+        <v>0</v>
+      </c>
+      <c r="E532" s="5">
+        <v>11072.43</v>
+      </c>
+      <c r="F532" s="6">
+        <f t="shared" ref="F532" si="93">F531-D532+E532</f>
+        <v>391174.94379200041</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="957" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2574D36B-E1ED-43BB-8D5A-8B07275B197F}"/>
+  <xr:revisionPtr revIDLastSave="959" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9079248-D6CB-434C-AE83-3F4011EE1303}"/>
   <bookViews>
-    <workbookView xWindow="13104" yWindow="1704" windowWidth="10068" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="2136" windowWidth="11556" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -985,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H532"/>
+  <dimension ref="A1:H533"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12051,8 +12051,26 @@
         <v>11072.43</v>
       </c>
       <c r="F532" s="6">
-        <f t="shared" ref="F532" si="93">F531-D532+E532</f>
+        <f t="shared" ref="F532:F533" si="93">F531-D532+E532</f>
         <v>391174.94379200041</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B533" s="28">
+        <v>46095</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D533" s="5">
+        <v>20</v>
+      </c>
+      <c r="E533" s="5">
+        <v>0</v>
+      </c>
+      <c r="F533" s="6">
+        <f t="shared" si="93"/>
+        <v>391154.94379200041</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="959" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9079248-D6CB-434C-AE83-3F4011EE1303}"/>
+  <xr:revisionPtr revIDLastSave="969" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9323BDCE-36D6-4C73-A6FA-F85E0D9D25A7}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="2136" windowWidth="11556" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1476" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -536,7 +536,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="\฿#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;฿&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$-1010000]d/m/yyyy;@"/>
@@ -546,6 +546,7 @@
     <numFmt numFmtId="170" formatCode="[$฿-41E]#,##0.00"/>
     <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -643,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -677,6 +678,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H533"/>
+  <dimension ref="A1:H536"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12051,7 +12053,7 @@
         <v>11072.43</v>
       </c>
       <c r="F532" s="6">
-        <f t="shared" ref="F532:F533" si="93">F531-D532+E532</f>
+        <f t="shared" ref="F532:F534" si="93">F531-D532+E532</f>
         <v>391174.94379200041</v>
       </c>
     </row>
@@ -12072,6 +12074,64 @@
         <f t="shared" si="93"/>
         <v>391154.94379200041</v>
       </c>
+    </row>
+    <row r="534" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A534" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B534" s="28">
+        <v>46097</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D534" s="5">
+        <v>432</v>
+      </c>
+      <c r="E534" s="5">
+        <v>0</v>
+      </c>
+      <c r="F534" s="6">
+        <f t="shared" si="93"/>
+        <v>390722.94379200041</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B535" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D535" s="5">
+        <v>0</v>
+      </c>
+      <c r="E535" s="5">
+        <v>2181.6</v>
+      </c>
+      <c r="F535" s="6">
+        <f t="shared" ref="F535" si="94">F534-D535+E535</f>
+        <v>392904.54379200039</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B536" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D536" s="5">
+        <v>0</v>
+      </c>
+      <c r="E536" s="5">
+        <v>1496</v>
+      </c>
+      <c r="F536" s="6">
+        <f t="shared" ref="F536" si="95">F535-D536+E536</f>
+        <v>394400.54379200039</v>
+      </c>
+      <c r="G536" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="969" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9323BDCE-36D6-4C73-A6FA-F85E0D9D25A7}"/>
+  <xr:revisionPtr revIDLastSave="974" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABAF40D4-941A-43D6-8417-E0CFEB27ECED}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1476" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="1308" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -696,10 +696,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -987,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H536"/>
+  <dimension ref="A1:H537"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12098,20 +12094,20 @@
     </row>
     <row r="535" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B535" s="28">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D535" s="5">
         <v>0</v>
       </c>
       <c r="E535" s="5">
-        <v>2181.6</v>
+        <v>2194.1999999999998</v>
       </c>
       <c r="F535" s="6">
-        <f t="shared" ref="F535" si="94">F534-D535+E535</f>
-        <v>392904.54379200039</v>
+        <f t="shared" ref="F535:F537" si="94">F533-D535+E535</f>
+        <v>393349.14379200042</v>
       </c>
     </row>
     <row r="536" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12125,13 +12121,31 @@
         <v>0</v>
       </c>
       <c r="E536" s="5">
+        <v>2181.6</v>
+      </c>
+      <c r="F536" s="6">
+        <f t="shared" si="94"/>
+        <v>392904.54379200039</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B537" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D537" s="5">
+        <v>0</v>
+      </c>
+      <c r="E537" s="5">
         <v>1496</v>
       </c>
-      <c r="F536" s="6">
-        <f t="shared" ref="F536" si="95">F535-D536+E536</f>
-        <v>394400.54379200039</v>
-      </c>
-      <c r="G536" s="33"/>
+      <c r="F537" s="6">
+        <f t="shared" si="94"/>
+        <v>394845.14379200042</v>
+      </c>
+      <c r="G537" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="974" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABAF40D4-941A-43D6-8417-E0CFEB27ECED}"/>
+  <xr:revisionPtr revIDLastSave="980" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBA2C302-E464-4B93-9DFE-889A67BCAB4F}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="1308" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1476" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -696,6 +696,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -983,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H537"/>
+  <dimension ref="A1:H538"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12049,7 +12053,7 @@
         <v>11072.43</v>
       </c>
       <c r="F532" s="6">
-        <f t="shared" ref="F532:F534" si="93">F531-D532+E532</f>
+        <f t="shared" ref="F532:F538" si="93">F531-D532+E532</f>
         <v>391174.94379200041</v>
       </c>
     </row>
@@ -12106,8 +12110,8 @@
         <v>2194.1999999999998</v>
       </c>
       <c r="F535" s="6">
-        <f t="shared" ref="F535:F537" si="94">F533-D535+E535</f>
-        <v>393349.14379200042</v>
+        <f t="shared" si="93"/>
+        <v>392917.14379200042</v>
       </c>
     </row>
     <row r="536" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12124,8 +12128,8 @@
         <v>2181.6</v>
       </c>
       <c r="F536" s="6">
-        <f t="shared" si="94"/>
-        <v>392904.54379200039</v>
+        <f t="shared" si="93"/>
+        <v>395098.7437920004</v>
       </c>
     </row>
     <row r="537" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12142,10 +12146,28 @@
         <v>1496</v>
       </c>
       <c r="F537" s="6">
-        <f t="shared" si="94"/>
-        <v>394845.14379200042</v>
+        <f t="shared" si="93"/>
+        <v>396594.7437920004</v>
       </c>
       <c r="G537" s="33"/>
+    </row>
+    <row r="538" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B538" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D538" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E538" s="5">
+        <v>0</v>
+      </c>
+      <c r="F538" s="30">
+        <f t="shared" si="93"/>
+        <v>386594.7437920004</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="980" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBA2C302-E464-4B93-9DFE-889A67BCAB4F}"/>
+  <xr:revisionPtr revIDLastSave="988" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93408B8-76FD-4121-82E5-9B45646E6A50}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1476" windowWidth="10992" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1596" windowWidth="16332" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -537,16 +537,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="[$-1010000]d/m/yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="170" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="187" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="188" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="190" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="191" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="192" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="193" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="194" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="195" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="196" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -599,7 +599,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -619,7 +619,7 @@
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -647,38 +647,38 @@
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="196" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,10 +694,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H538"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12167,6 +12163,42 @@
       <c r="F538" s="30">
         <f t="shared" si="93"/>
         <v>386594.7437920004</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B539" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D539" s="5">
+        <v>0</v>
+      </c>
+      <c r="E539" s="5">
+        <v>19865.34</v>
+      </c>
+      <c r="F539" s="6">
+        <f t="shared" ref="F539" si="94">F538-D539+E539</f>
+        <v>406460.08379200043</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B540" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D540" s="5">
+        <v>6035.04</v>
+      </c>
+      <c r="E540" s="5">
+        <v>0</v>
+      </c>
+      <c r="F540" s="6">
+        <f t="shared" ref="F540" si="95">F539-D540+E540</f>
+        <v>400425.04379200045</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="988" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93408B8-76FD-4121-82E5-9B45646E6A50}"/>
+  <xr:revisionPtr revIDLastSave="991" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C39D12-6996-4912-8B31-B3FF9D5984F8}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1596" windowWidth="16332" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="9924" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -696,6 +696,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -983,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H541"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12197,8 +12201,26 @@
         <v>0</v>
       </c>
       <c r="F540" s="6">
-        <f t="shared" ref="F540" si="95">F539-D540+E540</f>
+        <f t="shared" ref="F540:F541" si="95">F539-D540+E540</f>
         <v>400425.04379200045</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B541" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D541" s="5">
+        <v>0</v>
+      </c>
+      <c r="E541" s="5">
+        <v>7897.5</v>
+      </c>
+      <c r="F541" s="6">
+        <f t="shared" si="95"/>
+        <v>408322.54379200045</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="991" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C39D12-6996-4912-8B31-B3FF9D5984F8}"/>
+  <xr:revisionPtr revIDLastSave="996" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9DC1770-94BD-41C9-ADD8-8551645187F8}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="9924" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1476" windowWidth="15552" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="160">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -537,16 +537,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="187" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="188" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="[$-1010000]d/m/yyyy;@"/>
-    <numFmt numFmtId="190" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="191" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="192" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="193" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="194" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="195" formatCode="#,##0.00000000000"/>
-    <numFmt numFmtId="196" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="170" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -599,7 +599,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -619,7 +619,7 @@
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -647,38 +647,38 @@
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="196" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,10 +694,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H541"/>
+  <dimension ref="A1:H542"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12201,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="F540" s="6">
-        <f t="shared" ref="F540:F541" si="95">F539-D540+E540</f>
+        <f t="shared" ref="F540:F542" si="95">F539-D540+E540</f>
         <v>400425.04379200045</v>
       </c>
     </row>
@@ -12218,9 +12214,30 @@
       <c r="E541" s="5">
         <v>7897.5</v>
       </c>
-      <c r="F541" s="6">
+      <c r="F541" s="30">
         <f t="shared" si="95"/>
         <v>408322.54379200045</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A542" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B542" s="28">
+        <v>46113</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D542" s="5">
+        <v>1057.6300000000001</v>
+      </c>
+      <c r="E542" s="5">
+        <v>0</v>
+      </c>
+      <c r="F542" s="6">
+        <f t="shared" si="95"/>
+        <v>407264.91379200044</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="996" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9DC1770-94BD-41C9-ADD8-8551645187F8}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5664C5B1-035B-430E-8DB3-2EFF8AB63F66}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1476" windowWidth="15552" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="876" windowWidth="18036" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="161">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -531,22 +531,25 @@
   <si>
     <t xml:space="preserve">SCC </t>
   </si>
+  <si>
+    <t>Regent A/C</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="[$-1010000]d/m/yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="170" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="187" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="188" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="190" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="191" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="192" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="193" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="194" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="195" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="196" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -599,7 +602,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -619,7 +622,7 @@
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -647,38 +650,38 @@
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="196" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,6 +697,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -983,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H542"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12238,6 +12245,27 @@
       <c r="F542" s="6">
         <f t="shared" si="95"/>
         <v>407264.91379200044</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A543" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B543" s="28">
+        <v>46115</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D543" s="5">
+        <v>14900</v>
+      </c>
+      <c r="E543" s="5">
+        <v>0</v>
+      </c>
+      <c r="F543" s="6">
+        <f t="shared" ref="F543" si="96">F542-D543+E543</f>
+        <v>392364.91379200044</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5664C5B1-035B-430E-8DB3-2EFF8AB63F66}"/>
+  <xr:revisionPtr revIDLastSave="1115" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{688A16A4-BD58-47DC-A236-D49DBA6CE292}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="876" windowWidth="18036" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1116" windowWidth="10068" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="161">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -539,17 +539,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
-    <numFmt numFmtId="187" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="188" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="[$-1010000]d/m/yyyy;@"/>
-    <numFmt numFmtId="190" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="191" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="192" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="193" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="194" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="195" formatCode="#,##0.00000000000"/>
-    <numFmt numFmtId="196" formatCode="#,##0.0"/>
+  <numFmts count="11">
+    <numFmt numFmtId="164" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$-1010000]d/m/yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="170" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0000000000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -602,7 +603,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -622,17 +623,23 @@
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -647,41 +654,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="192" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="196" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,10 +707,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -990,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:H568"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12264,8 +12270,500 @@
         <v>0</v>
       </c>
       <c r="F543" s="6">
-        <f t="shared" ref="F543" si="96">F542-D543+E543</f>
+        <f t="shared" ref="F543:F561" si="96">F542-D543+E543</f>
         <v>392364.91379200044</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B544" s="28">
+        <v>46121</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D544" s="5">
+        <v>20</v>
+      </c>
+      <c r="E544" s="5">
+        <v>0</v>
+      </c>
+      <c r="F544" s="6">
+        <f t="shared" si="96"/>
+        <v>392344.91379200044</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A545" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B545" s="28">
+        <v>46128</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D545" s="5">
+        <v>331.78</v>
+      </c>
+      <c r="E545" s="5">
+        <v>0</v>
+      </c>
+      <c r="F545" s="6">
+        <f t="shared" si="96"/>
+        <v>392013.13379200042</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A546" s="28">
+        <v>46134</v>
+      </c>
+      <c r="B546" s="28">
+        <v>46136</v>
+      </c>
+      <c r="C546" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D546" s="32">
+        <v>70155.039999999994</v>
+      </c>
+      <c r="E546" s="7">
+        <v>0</v>
+      </c>
+      <c r="F546" s="6">
+        <f t="shared" si="96"/>
+        <v>321858.09379200044</v>
+      </c>
+      <c r="G546" s="22"/>
+    </row>
+    <row r="547" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A547" s="28">
+        <v>46134</v>
+      </c>
+      <c r="B547" s="28">
+        <v>46136</v>
+      </c>
+      <c r="C547" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D547" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E547" s="5">
+        <v>0</v>
+      </c>
+      <c r="F547" s="6">
+        <f t="shared" si="96"/>
+        <v>321843.11379200045</v>
+      </c>
+      <c r="G547" s="22"/>
+    </row>
+    <row r="548" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B548" s="28">
+        <v>46136</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D548" s="5">
+        <v>0</v>
+      </c>
+      <c r="E548" s="5">
+        <v>2700</v>
+      </c>
+      <c r="F548" s="6">
+        <f t="shared" si="96"/>
+        <v>324543.11379200045</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B549" s="28">
+        <v>46140</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D549" s="5">
+        <v>0</v>
+      </c>
+      <c r="E549" s="5">
+        <v>9472.5</v>
+      </c>
+      <c r="F549" s="6">
+        <f t="shared" si="96"/>
+        <v>334015.61379200045</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A550" s="28">
+        <v>46139</v>
+      </c>
+      <c r="B550" s="28">
+        <v>46141</v>
+      </c>
+      <c r="C550" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D550" s="32">
+        <v>40088.6</v>
+      </c>
+      <c r="E550" s="7">
+        <v>0</v>
+      </c>
+      <c r="F550" s="6">
+        <f t="shared" si="96"/>
+        <v>293927.01379200048</v>
+      </c>
+      <c r="G550" s="22"/>
+    </row>
+    <row r="551" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A551" s="28">
+        <v>46139</v>
+      </c>
+      <c r="B551" s="28">
+        <v>46141</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D551" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E551" s="5">
+        <v>0</v>
+      </c>
+      <c r="F551" s="6">
+        <f t="shared" si="96"/>
+        <v>293912.0337920005</v>
+      </c>
+      <c r="G551" s="22"/>
+    </row>
+    <row r="552" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B552" s="28">
+        <v>46143</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D552" s="5">
+        <v>23000</v>
+      </c>
+      <c r="E552" s="5">
+        <v>0</v>
+      </c>
+      <c r="F552" s="6">
+        <f t="shared" si="96"/>
+        <v>270912.0337920005</v>
+      </c>
+      <c r="H552" s="36"/>
+    </row>
+    <row r="553" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A553" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B553" s="28">
+        <v>46144</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D553" s="34">
+        <v>1978.79</v>
+      </c>
+      <c r="E553" s="5">
+        <v>0</v>
+      </c>
+      <c r="F553" s="6">
+        <f t="shared" si="96"/>
+        <v>268933.24379200052</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B554" s="28">
+        <v>46148</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D554" s="5">
+        <v>0</v>
+      </c>
+      <c r="E554" s="34">
+        <v>2709</v>
+      </c>
+      <c r="F554" s="6">
+        <f t="shared" si="96"/>
+        <v>271642.24379200052</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A555" s="28">
+        <v>46142</v>
+      </c>
+      <c r="B555" s="28">
+        <v>46148</v>
+      </c>
+      <c r="C555" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D555" s="35">
+        <v>34075.306599999996</v>
+      </c>
+      <c r="E555" s="7">
+        <v>0</v>
+      </c>
+      <c r="F555" s="6">
+        <f t="shared" si="96"/>
+        <v>237566.93719200051</v>
+      </c>
+      <c r="G555" s="22"/>
+    </row>
+    <row r="556" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A556" s="28">
+        <v>46142</v>
+      </c>
+      <c r="B556" s="28">
+        <v>46148</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D556" s="34">
+        <v>14.98</v>
+      </c>
+      <c r="E556" s="5">
+        <v>0</v>
+      </c>
+      <c r="F556" s="6">
+        <f t="shared" si="96"/>
+        <v>237551.9571920005</v>
+      </c>
+      <c r="G556" s="22"/>
+    </row>
+    <row r="557" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B557" s="28">
+        <v>46149</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D557" s="5">
+        <v>0</v>
+      </c>
+      <c r="E557" s="34">
+        <v>51975</v>
+      </c>
+      <c r="F557" s="6">
+        <f t="shared" si="96"/>
+        <v>289526.95719200047</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B558" s="28">
+        <v>46149</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D558" s="5">
+        <v>0</v>
+      </c>
+      <c r="E558" s="34">
+        <v>7020</v>
+      </c>
+      <c r="F558" s="6">
+        <f t="shared" si="96"/>
+        <v>296546.95719200047</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B559" s="28">
+        <v>46150</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D559" s="5">
+        <v>0</v>
+      </c>
+      <c r="E559" s="34">
+        <v>4500</v>
+      </c>
+      <c r="F559" s="6">
+        <f t="shared" si="96"/>
+        <v>301046.95719200047</v>
+      </c>
+      <c r="H559" s="36"/>
+    </row>
+    <row r="560" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B560" s="28">
+        <v>46151</v>
+      </c>
+      <c r="C560" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D560" s="5">
+        <v>20</v>
+      </c>
+      <c r="E560" s="5">
+        <v>0</v>
+      </c>
+      <c r="F560" s="6">
+        <f t="shared" si="96"/>
+        <v>301026.95719200047</v>
+      </c>
+      <c r="H560" s="36"/>
+    </row>
+    <row r="561" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B561" s="28">
+        <v>46153</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D561" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E561" s="5">
+        <v>0</v>
+      </c>
+      <c r="F561" s="6">
+        <f t="shared" si="96"/>
+        <v>286026.95719200047</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B562" s="28">
+        <v>46154</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D562" s="5">
+        <v>0</v>
+      </c>
+      <c r="E562" s="5">
+        <v>5985</v>
+      </c>
+      <c r="F562" s="6">
+        <f t="shared" ref="F562:F568" si="97">F561-D562+E562</f>
+        <v>292011.95719200047</v>
+      </c>
+      <c r="H562" s="36"/>
+    </row>
+    <row r="563" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B563" s="28">
+        <v>46155</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D563" s="5">
+        <v>0</v>
+      </c>
+      <c r="E563" s="5">
+        <v>38898.639999999999</v>
+      </c>
+      <c r="F563" s="6">
+        <f t="shared" si="97"/>
+        <v>330910.59719200048</v>
+      </c>
+      <c r="H563" s="36"/>
+    </row>
+    <row r="564" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B564" s="28">
+        <v>46156</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D564" s="5">
+        <v>3360</v>
+      </c>
+      <c r="E564" s="5">
+        <v>0</v>
+      </c>
+      <c r="F564" s="6">
+        <f t="shared" si="97"/>
+        <v>327550.59719200048</v>
+      </c>
+      <c r="H564" s="36"/>
+    </row>
+    <row r="565" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B565" s="28">
+        <v>46157</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D565" s="5">
+        <v>0</v>
+      </c>
+      <c r="E565" s="5">
+        <v>1134</v>
+      </c>
+      <c r="F565" s="6">
+        <f t="shared" si="97"/>
+        <v>328684.59719200048</v>
+      </c>
+      <c r="H565" s="36"/>
+    </row>
+    <row r="566" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B566" s="28">
+        <v>46157</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D566" s="5">
+        <v>0</v>
+      </c>
+      <c r="E566" s="5">
+        <v>38340</v>
+      </c>
+      <c r="F566" s="6">
+        <f t="shared" si="97"/>
+        <v>367024.59719200048</v>
+      </c>
+      <c r="H566" s="36"/>
+    </row>
+    <row r="567" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B567" s="28">
+        <v>46157</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D567" s="5">
+        <v>0</v>
+      </c>
+      <c r="E567" s="5">
+        <v>4272</v>
+      </c>
+      <c r="F567" s="6">
+        <f t="shared" si="97"/>
+        <v>371296.59719200048</v>
+      </c>
+      <c r="H567" s="36"/>
+    </row>
+    <row r="568" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A568" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B568" s="28">
+        <v>46157</v>
+      </c>
+      <c r="C568" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D568" s="5">
+        <v>432</v>
+      </c>
+      <c r="E568" s="5">
+        <v>0</v>
+      </c>
+      <c r="F568" s="6">
+        <f t="shared" si="97"/>
+        <v>370864.59719200048</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1115" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{688A16A4-BD58-47DC-A236-D49DBA6CE292}"/>
+  <xr:revisionPtr revIDLastSave="1149" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEFABE62-B3D4-4D35-AEF6-A0BC36F832C6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1116" windowWidth="10068" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11400" yWindow="1692" windowWidth="10044" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="161">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -709,6 +709,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -996,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H568"/>
+  <dimension ref="A1:H578"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12765,6 +12769,208 @@
         <f t="shared" si="97"/>
         <v>370864.59719200048</v>
       </c>
+    </row>
+    <row r="569" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B569" s="28">
+        <v>46164</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D569" s="5">
+        <v>0</v>
+      </c>
+      <c r="E569" s="5">
+        <v>526.79999999999995</v>
+      </c>
+      <c r="F569" s="6">
+        <f t="shared" ref="F569" si="98">F568-D569+E569</f>
+        <v>371391.39719200047</v>
+      </c>
+      <c r="H569" s="36"/>
+    </row>
+    <row r="570" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B570" s="28">
+        <v>46164</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D570" s="5">
+        <v>0</v>
+      </c>
+      <c r="E570" s="5">
+        <v>1080</v>
+      </c>
+      <c r="F570" s="6">
+        <f t="shared" ref="F570:F576" si="99">F569-D570+E570</f>
+        <v>372471.39719200047</v>
+      </c>
+      <c r="H570" s="36"/>
+    </row>
+    <row r="571" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B571" s="28">
+        <v>46164</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D571" s="5">
+        <v>0</v>
+      </c>
+      <c r="E571" s="5">
+        <v>2250</v>
+      </c>
+      <c r="F571" s="6">
+        <f t="shared" si="99"/>
+        <v>374721.39719200047</v>
+      </c>
+      <c r="H571" s="36"/>
+    </row>
+    <row r="572" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B572" s="28">
+        <v>46164</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D572" s="5">
+        <v>0</v>
+      </c>
+      <c r="E572" s="5">
+        <v>1134</v>
+      </c>
+      <c r="F572" s="6">
+        <f t="shared" si="99"/>
+        <v>375855.39719200047</v>
+      </c>
+      <c r="H572" s="36"/>
+    </row>
+    <row r="573" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B573" s="28">
+        <v>46167</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D573" s="5">
+        <v>0</v>
+      </c>
+      <c r="E573" s="5">
+        <v>13068.88</v>
+      </c>
+      <c r="F573" s="6">
+        <f t="shared" ref="F573:F578" si="100">F572-D573+E573</f>
+        <v>388924.27719200047</v>
+      </c>
+      <c r="H573" s="36"/>
+    </row>
+    <row r="574" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A574" s="28">
+        <v>46163</v>
+      </c>
+      <c r="B574" s="28">
+        <v>46167</v>
+      </c>
+      <c r="C574" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D574" s="32">
+        <v>10282.73</v>
+      </c>
+      <c r="E574" s="7">
+        <v>0</v>
+      </c>
+      <c r="F574" s="6">
+        <f t="shared" si="100"/>
+        <v>378641.54719200049</v>
+      </c>
+      <c r="G574" s="22"/>
+    </row>
+    <row r="575" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="28">
+        <v>46163</v>
+      </c>
+      <c r="B575" s="28">
+        <v>46167</v>
+      </c>
+      <c r="C575" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D575" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E575" s="5">
+        <v>0</v>
+      </c>
+      <c r="F575" s="6">
+        <f t="shared" si="100"/>
+        <v>378626.56719200051</v>
+      </c>
+      <c r="G575" s="22"/>
+    </row>
+    <row r="576" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B576" s="28">
+        <v>46168</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D576" s="5">
+        <v>0</v>
+      </c>
+      <c r="E576" s="5">
+        <v>351</v>
+      </c>
+      <c r="F576" s="6">
+        <f t="shared" si="100"/>
+        <v>378977.56719200051</v>
+      </c>
+      <c r="H576" s="36"/>
+    </row>
+    <row r="577" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A577" s="28">
+        <v>46164</v>
+      </c>
+      <c r="B577" s="28">
+        <v>46168</v>
+      </c>
+      <c r="C577" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D577" s="32">
+        <v>103057.76</v>
+      </c>
+      <c r="E577" s="7">
+        <v>0</v>
+      </c>
+      <c r="F577" s="6">
+        <f t="shared" si="100"/>
+        <v>275919.8071920005</v>
+      </c>
+      <c r="G577" s="22"/>
+    </row>
+    <row r="578" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A578" s="28">
+        <v>46164</v>
+      </c>
+      <c r="B578" s="28">
+        <v>46168</v>
+      </c>
+      <c r="C578" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D578" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E578" s="5">
+        <v>0</v>
+      </c>
+      <c r="F578" s="6">
+        <f t="shared" si="100"/>
+        <v>275904.82719200052</v>
+      </c>
+      <c r="G578" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1149" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEFABE62-B3D4-4D35-AEF6-A0BC36F832C6}"/>
+  <xr:revisionPtr revIDLastSave="1254" documentId="13_ncr:1_{B3FB09C8-509C-4800-A6F5-97AF885696E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC2C3EF-E5FD-4A4E-A6B8-BAACBD882683}"/>
   <bookViews>
-    <workbookView xWindow="11400" yWindow="1692" windowWidth="10044" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="1476" windowWidth="15996" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="164">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -534,6 +534,15 @@
   <si>
     <t>Regent A/C</t>
   </si>
+  <si>
+    <t>PROSPECT</t>
+  </si>
+  <si>
+    <t>lenovo</t>
+  </si>
+  <si>
+    <t>PROSPECT-Div</t>
+  </si>
 </sst>
 </file>
 
@@ -1000,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H578"/>
+  <dimension ref="A1:H604"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" style="29" bestFit="1" customWidth="1"/>
@@ -12803,7 +12812,7 @@
         <v>1080</v>
       </c>
       <c r="F570" s="6">
-        <f t="shared" ref="F570:F576" si="99">F569-D570+E570</f>
+        <f t="shared" ref="F570:F572" si="99">F569-D570+E570</f>
         <v>372471.39719200047</v>
       </c>
       <c r="H570" s="36"/>
@@ -12928,7 +12937,7 @@
       </c>
       <c r="H576" s="36"/>
     </row>
-    <row r="577" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="28">
         <v>46164</v>
       </c>
@@ -12950,7 +12959,7 @@
       </c>
       <c r="G577" s="22"/>
     </row>
-    <row r="578" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="28">
         <v>46164</v>
       </c>
@@ -12971,6 +12980,514 @@
         <v>275904.82719200052</v>
       </c>
       <c r="G578" s="22"/>
+    </row>
+    <row r="579" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B579" s="28">
+        <v>46170</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D579" s="5">
+        <v>0</v>
+      </c>
+      <c r="E579" s="5">
+        <v>648</v>
+      </c>
+      <c r="F579" s="6">
+        <f t="shared" ref="F579" si="101">F578-D579+E579</f>
+        <v>276552.82719200052</v>
+      </c>
+      <c r="H579" s="36"/>
+    </row>
+    <row r="580" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B580" s="28">
+        <v>46170</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D580" s="5">
+        <v>0</v>
+      </c>
+      <c r="E580" s="5">
+        <v>2205</v>
+      </c>
+      <c r="F580" s="6">
+        <f t="shared" ref="F580" si="102">F579-D580+E580</f>
+        <v>278757.82719200052</v>
+      </c>
+      <c r="H580" s="36"/>
+    </row>
+    <row r="581" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B581" s="28">
+        <v>46173</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D581" s="5">
+        <v>24400</v>
+      </c>
+      <c r="E581" s="5">
+        <v>0</v>
+      </c>
+      <c r="F581" s="6">
+        <f t="shared" ref="F581:F584" si="103">F580-D581+E581</f>
+        <v>254357.82719200052</v>
+      </c>
+      <c r="H581" s="36"/>
+    </row>
+    <row r="582" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A582" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B582" s="28">
+        <v>46175</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D582" s="34">
+        <v>1372.91</v>
+      </c>
+      <c r="E582" s="5">
+        <v>0</v>
+      </c>
+      <c r="F582" s="6">
+        <f t="shared" si="103"/>
+        <v>252984.91719200052</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B583" s="28">
+        <v>46176</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D583" s="5">
+        <v>1900</v>
+      </c>
+      <c r="E583" s="5">
+        <v>0</v>
+      </c>
+      <c r="F583" s="6">
+        <f t="shared" si="103"/>
+        <v>251084.91719200052</v>
+      </c>
+      <c r="H583" s="36"/>
+    </row>
+    <row r="584" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B584" s="28">
+        <v>46177</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D584" s="5">
+        <v>0</v>
+      </c>
+      <c r="E584" s="5">
+        <v>21000</v>
+      </c>
+      <c r="F584" s="6">
+        <f t="shared" si="103"/>
+        <v>272084.91719200055</v>
+      </c>
+      <c r="H584" s="36"/>
+    </row>
+    <row r="585" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B585" s="28">
+        <v>46178</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D585" s="5">
+        <v>4200</v>
+      </c>
+      <c r="E585" s="5">
+        <v>0</v>
+      </c>
+      <c r="F585" s="30">
+        <f t="shared" ref="F585:F586" si="104">F584-D585+E585</f>
+        <v>267884.91719200055</v>
+      </c>
+      <c r="H585" s="36"/>
+    </row>
+    <row r="586" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B586" s="28">
+        <v>46178</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D586" s="5">
+        <v>0</v>
+      </c>
+      <c r="E586" s="5">
+        <v>3447</v>
+      </c>
+      <c r="F586" s="6">
+        <f t="shared" si="104"/>
+        <v>271331.91719200055</v>
+      </c>
+      <c r="H586" s="36"/>
+    </row>
+    <row r="587" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B587" s="28">
+        <v>46183</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D587" s="5">
+        <v>0</v>
+      </c>
+      <c r="E587" s="5">
+        <v>166.05</v>
+      </c>
+      <c r="F587" s="6">
+        <f t="shared" ref="F587" si="105">F586-D587+E587</f>
+        <v>271497.96719200053</v>
+      </c>
+      <c r="H587" s="36"/>
+    </row>
+    <row r="588" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B588" s="28">
+        <v>46183</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D588" s="5">
+        <v>0</v>
+      </c>
+      <c r="E588" s="5">
+        <v>8999.1</v>
+      </c>
+      <c r="F588" s="6">
+        <f t="shared" ref="F588" si="106">F587-D588+E588</f>
+        <v>280497.06719200051</v>
+      </c>
+      <c r="H588" s="36"/>
+    </row>
+    <row r="589" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B589" s="28">
+        <v>46184</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D589" s="5">
+        <v>0</v>
+      </c>
+      <c r="E589" s="5">
+        <v>12084.66</v>
+      </c>
+      <c r="F589" s="6">
+        <f t="shared" ref="F589" si="107">F588-D589+E589</f>
+        <v>292581.72719200049</v>
+      </c>
+      <c r="H589" s="36"/>
+    </row>
+    <row r="590" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B590" s="28">
+        <v>46184</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D590" s="5">
+        <v>0</v>
+      </c>
+      <c r="E590" s="5">
+        <v>19908</v>
+      </c>
+      <c r="F590" s="6">
+        <f t="shared" ref="F590" si="108">F589-D590+E590</f>
+        <v>312489.72719200049</v>
+      </c>
+      <c r="H590" s="36"/>
+    </row>
+    <row r="591" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B591" s="28">
+        <v>46184</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D591" s="5">
+        <v>6048</v>
+      </c>
+      <c r="E591" s="5">
+        <v>0</v>
+      </c>
+      <c r="F591" s="30">
+        <f t="shared" ref="F591:F600" si="109">F590-D591+E591</f>
+        <v>306441.72719200049</v>
+      </c>
+      <c r="H591" s="36"/>
+    </row>
+    <row r="592" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B592" s="28">
+        <v>46185</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D592" s="5">
+        <v>0</v>
+      </c>
+      <c r="E592" s="5">
+        <v>1134</v>
+      </c>
+      <c r="F592" s="6">
+        <f t="shared" si="109"/>
+        <v>307575.72719200049</v>
+      </c>
+      <c r="H592" s="36"/>
+    </row>
+    <row r="593" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A593" s="28">
+        <v>46183</v>
+      </c>
+      <c r="B593" s="28">
+        <v>46185</v>
+      </c>
+      <c r="C593" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D593" s="32">
+        <v>188416.4</v>
+      </c>
+      <c r="E593" s="7">
+        <v>0</v>
+      </c>
+      <c r="F593" s="6">
+        <f t="shared" si="109"/>
+        <v>119159.32719200049</v>
+      </c>
+      <c r="G593" s="22"/>
+    </row>
+    <row r="594" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A594" s="28">
+        <v>46183</v>
+      </c>
+      <c r="B594" s="28">
+        <v>46185</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D594" s="5">
+        <v>14.98</v>
+      </c>
+      <c r="E594" s="5">
+        <v>0</v>
+      </c>
+      <c r="F594" s="6">
+        <f t="shared" si="109"/>
+        <v>119144.3471920005</v>
+      </c>
+      <c r="G594" s="22"/>
+    </row>
+    <row r="595" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B595" s="28">
+        <v>46186</v>
+      </c>
+      <c r="C595" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D595" s="5">
+        <v>20</v>
+      </c>
+      <c r="E595" s="5">
+        <v>0</v>
+      </c>
+      <c r="F595" s="6">
+        <f t="shared" si="109"/>
+        <v>119124.3471920005</v>
+      </c>
+      <c r="H595" s="36"/>
+    </row>
+    <row r="596" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A596" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B596" s="28">
+        <v>46188</v>
+      </c>
+      <c r="C596" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D596" s="5">
+        <v>432</v>
+      </c>
+      <c r="E596" s="5">
+        <v>0</v>
+      </c>
+      <c r="F596" s="6">
+        <f t="shared" si="109"/>
+        <v>118692.3471920005</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B597" s="28">
+        <v>46189</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D597" s="5">
+        <v>0</v>
+      </c>
+      <c r="E597" s="5">
+        <v>2709</v>
+      </c>
+      <c r="F597" s="6">
+        <f t="shared" si="109"/>
+        <v>121401.3471920005</v>
+      </c>
+      <c r="H597" s="36"/>
+    </row>
+    <row r="598" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B598" s="28">
+        <v>46191</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D598" s="5">
+        <v>0</v>
+      </c>
+      <c r="E598" s="5">
+        <v>6453</v>
+      </c>
+      <c r="F598" s="30">
+        <f t="shared" si="109"/>
+        <v>127854.3471920005</v>
+      </c>
+      <c r="H598" s="36"/>
+    </row>
+    <row r="599" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A599" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B599" s="28">
+        <v>46205</v>
+      </c>
+      <c r="C599" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D599" s="34">
+        <v>357.35</v>
+      </c>
+      <c r="E599" s="5">
+        <v>0</v>
+      </c>
+      <c r="F599" s="6">
+        <f t="shared" si="109"/>
+        <v>127496.99719200049</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B600" s="28">
+        <v>46210</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D600" s="5">
+        <v>26000</v>
+      </c>
+      <c r="E600" s="5">
+        <v>0</v>
+      </c>
+      <c r="F600" s="6">
+        <f t="shared" si="109"/>
+        <v>101496.99719200049</v>
+      </c>
+      <c r="H600" s="36"/>
+    </row>
+    <row r="601" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B601" s="28">
+        <v>46214</v>
+      </c>
+      <c r="C601" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D601" s="5">
+        <v>20</v>
+      </c>
+      <c r="E601" s="5">
+        <v>0</v>
+      </c>
+      <c r="F601" s="6">
+        <f t="shared" ref="F601:F604" si="110">F600-D601+E601</f>
+        <v>101476.99719200049</v>
+      </c>
+      <c r="H601" s="36"/>
+    </row>
+    <row r="602" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B602" s="28">
+        <v>46214</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D602" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E602" s="5">
+        <v>0</v>
+      </c>
+      <c r="F602" s="6">
+        <f t="shared" si="110"/>
+        <v>81476.99719200049</v>
+      </c>
+      <c r="H602" s="36"/>
+    </row>
+    <row r="603" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A603" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B603" s="28">
+        <v>46218</v>
+      </c>
+      <c r="C603" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D603" s="5">
+        <v>432</v>
+      </c>
+      <c r="E603" s="5">
+        <v>0</v>
+      </c>
+      <c r="F603" s="6">
+        <f t="shared" si="110"/>
+        <v>81044.99719200049</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B604" s="28">
+        <v>46218</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D604" s="5">
+        <v>0</v>
+      </c>
+      <c r="E604" s="5">
+        <v>1278</v>
+      </c>
+      <c r="F604" s="30">
+        <f t="shared" si="110"/>
+        <v>82322.99719200049</v>
+      </c>
+      <c r="H604" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
